--- a/Fase 2/Evidencias Proyecto/Evidencias de Documentación/Matriz RACI CuTuCo.xlsx
+++ b/Fase 2/Evidencias Proyecto/Evidencias de Documentación/Matriz RACI CuTuCo.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ignac\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ignac\Videos\Inicio\Evidencias de Documentación\Documentos Actualizados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D84B9FAF-88AE-4450-851E-94BAABEFBACF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_BC1DE4706F38083764BAD76CBC43DB32204D1732" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,6 +16,10 @@
     <sheet name="Recursos x Actividad" sheetId="1" r:id="rId1"/>
     <sheet name="Instrucciones" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">Instrucciones!$A$1:$F$20</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Recursos x Actividad'!$A$1:$P$26</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -35,66 +39,6 @@
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="40">
-  <si>
-    <t>Proyecto CuTuCo | Equipo de desarrollo: Vicente Rivera (backend / líder) e Ignacio Fuenzalida (frontend) | 13 semanas desde el 11/09/2026 | Metodología tradicional en 4 fases</t>
-  </si>
-  <si>
-    <t>Actividad</t>
-  </si>
-  <si>
-    <t>Roles / Responsabilidades</t>
-  </si>
-  <si>
-    <t>ID Actividad</t>
-  </si>
-  <si>
-    <t>Vicente Rivera</t>
-  </si>
-  <si>
-    <t>Ignacio Fuenzalida</t>
-  </si>
-  <si>
-    <t>Fase 1 - Planificación inicial: Acta de Constitución, EDT, Hitos y Diccionario, Carta Gantt, RACI, Matriz de Riesgos y Plan de Pruebas Inicial (Semanas 1-2)</t>
-  </si>
-  <si>
-    <t>A/R</t>
-  </si>
-  <si>
-    <t>R</t>
-  </si>
-  <si>
-    <t>Fase 2 - ERS con el alcance actualizado (Queda / No queda), criterios de aceptación y Plan de Calidad y de Costos (Semanas 2-4)</t>
-  </si>
-  <si>
-    <t>Fase 2 - Modelo de datos (DER, tabla payouts, RLS) y arquitectura: Supabase (GoTrue, PostgREST), FastAPI y despliegue (Semanas 2-4)</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>Fase 2 - Mockups de interfaz en Vue.js: cliente, productor, administración, checkout y entrega (Semanas 3-4)</t>
-  </si>
-  <si>
-    <t>Fase 3 - Backend: autenticación con GoTrue, bloqueo tras 5 intentos, reglas de negocio y pagos en FastAPI, entrega con código (Semanas 4-10)</t>
-  </si>
-  <si>
-    <t>Fase 3 - Frontend: Vue.js/Vite, catálogo invitado, carrito, panel del productor, administración, checkout y seguimiento (Semanas 4-10)</t>
-  </si>
-  <si>
-    <t>Fase 3 - Base de datos e integraciones: migración SQLite a PostgreSQL, scripts DDL, payouts, Webpay Plus Test y correos con Resend (Semanas 4-10)</t>
-  </si>
-  <si>
-    <t>Fase 3/4 - Pruebas por capas y E2E, minuta de control, verificación de alcances y corrección de defectos (Semanas 7-11)</t>
-  </si>
-  <si>
-    <t>Fase 4 - Despliegue (Vercel, Cloud Run, Supabase), Plan de Implantación, Soporte y Mantenimiento y Manuales de Usuario y Administrador (Semanas 11-12)</t>
-  </si>
-  <si>
-    <t>Fase 4 - Plan de Pruebas Final, Reporte de Estatus Final, cierre y preparación de la entrega final (Semanas 12-13)</t>
-  </si>
-  <si>
-    <t>Criterio de asignación: somos dos personas y repartimos las responsabilidades según la especialidad de cada uno. Vicente lidera backend, pagos, base de datos y las decisiones de proyecto; Ignacio lidera frontend, mockups y pantallas. Arquitectura, pruebas, documentación y control de cambios los trabajamos juntos. Como solo hay dos integrantes, usamos "A/R" cuando la misma persona ejecuta y aprueba, y "R" cuando el otro integrante también ejecuta. El alcance actualizado dejó fuera el historial de precios, los avisos de stock bajo, los múltiples administradores, la retención de carnet y el rate limiting, por lo que no tienen actividad propia. R = Responsable de ejecutar; A = Aprobador; C = Consultado; I = Informado.</t>
-  </si>
   <si>
     <t>Matriz de Asignación de Responsabilidades (RACI)</t>
   </si>
@@ -147,6 +91,9 @@
     <t>Aprobador: Es el encargado de aprobar (firmar), el trabajo realizado, a partir de esa aprobación, este se vuelve responsable por la actividad. Como regla general debe existir un solo "A" por actividad. Este rol es quien asegura que se ejecutan las tareas, por ejemplo Líderes de área técnica, área de gestión de proyecto, entre otros.</t>
   </si>
   <si>
+    <t>C</t>
+  </si>
+  <si>
     <t>Consultado: Posee alguna información o capacidad que se necesita para mantener el trabajo. Se le informa y consulta información, de manera bidireccional con el responsable y/o aprobador.</t>
   </si>
   <si>
@@ -154,6 +101,63 @@
   </si>
   <si>
     <t>Informado: Rol que debe ser informado sobre el progreso y los resultados del trabajo. En este caso la comunicación es unidireccional (se le da información pero no se recibe información).</t>
+  </si>
+  <si>
+    <t>Proyecto CuTuCo | Equipo de desarrollo: Vicente Rivera (backend / líder) e Ignacio Fuenzalida (frontend) | 13 semanas desde el 11/09/2026 | Metodología tradicional en 4 fases</t>
+  </si>
+  <si>
+    <t>Actividad</t>
+  </si>
+  <si>
+    <t>Roles / Responsabilidades</t>
+  </si>
+  <si>
+    <t>ID Actividad</t>
+  </si>
+  <si>
+    <t>Vicente Rivera</t>
+  </si>
+  <si>
+    <t>Ignacio Fuenzalida</t>
+  </si>
+  <si>
+    <t>Fase 1 - Planificación inicial: Acta de Constitución, EDT, Hitos y Diccionario, Carta Gantt, RACI, Matriz de Riesgos y Plan de Pruebas Inicial (Semanas 1-2)</t>
+  </si>
+  <si>
+    <t>A/R</t>
+  </si>
+  <si>
+    <t>R</t>
+  </si>
+  <si>
+    <t>Fase 2 - ERS con el alcance actualizado (Queda / No queda), criterios de aceptación y Plan de Calidad y de Costos (Semanas 2-4)</t>
+  </si>
+  <si>
+    <t>Fase 2 - Modelo de datos (DER, tablas productores y payments, RLS) y arquitectura: Supabase (GoTrue, PostgREST), FastAPI y despliegue (Semanas 2-4)</t>
+  </si>
+  <si>
+    <t>Fase 2 - Mockups de interfaz en Vue.js: cliente, productor, administración, checkout y entrega (Semanas 3-4)</t>
+  </si>
+  <si>
+    <t>Fase 3 - Backend: autenticación con GoTrue, bloqueo tras 5 intentos, reglas de negocio y pagos en FastAPI, entrega con código (Semanas 4-10)</t>
+  </si>
+  <si>
+    <t>Fase 3 - Frontend: Vue.js/Vite, catálogo invitado, carrito, panel del productor, administración, checkout y seguimiento (Semanas 4-10)</t>
+  </si>
+  <si>
+    <t>Fase 3 - Base de datos e integraciones: migración SQLite a PostgreSQL, scripts DDL, Webpay Mall (Split Payment) y correos con Resend (Semanas 4-10)</t>
+  </si>
+  <si>
+    <t>Fase 3/4 - Pruebas por capas y E2E, minuta de control, verificación de alcances y corrección de defectos (Semanas 7-11)</t>
+  </si>
+  <si>
+    <t>Fase 4 - Despliegue (Vercel, Cloud Run, Supabase), Plan de Implantación, Soporte y Mantenimiento y Manuales de Usuario y Administrador (Semanas 11-12)</t>
+  </si>
+  <si>
+    <t>Fase 4 - Plan de Pruebas Final, Reporte de Estatus Final, cierre y preparación de la entrega final (Semanas 12-13)</t>
+  </si>
+  <si>
+    <t>Criterio de asignación: somos dos personas y repartimos las responsabilidades según la especialidad de cada uno. Vicente lidera backend, pagos, base de datos y las decisiones de proyecto; Ignacio lidera frontend, mockups y pantallas. Arquitectura, pruebas, documentación y control de cambios los trabajamos juntos. Como solo hay dos integrantes, usamos "A/R" cuando la misma persona ejecuta y aprueba, y "R" cuando el otro integrante también ejecuta. El alcance actualizado dejó fuera el historial de precios, los avisos de stock bajo, los múltiples administradores, la retención de carnet y el rate limiting, por lo que no tienen actividad propia. La segunda redefinición de alcance reemplazó además el escrow manual y los payouts por Webpay Mall (Split Payment) con liquidación directa por pasarela, e incorporó la verificación documental KYB y el ingreso del Código de Comercio Mall en la aprobación de vendedores. R = Responsable de ejecutar; A = Aprobador; C = Consultado; I = Informado.</t>
   </si>
 </sst>
 </file>
@@ -407,17 +411,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -433,10 +426,6 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -449,14 +438,8 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -467,6 +450,27 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -680,6 +684,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:Z1000"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -691,7 +698,8 @@
     <col min="6" max="6" width="11.140625" style="5" customWidth="1"/>
     <col min="7" max="12" width="7" style="5" customWidth="1"/>
     <col min="13" max="26" width="10" style="5" customWidth="1"/>
-    <col min="27" max="16384" width="14.42578125" style="5"/>
+    <col min="27" max="27" width="14.42578125" style="5" customWidth="1"/>
+    <col min="28" max="16384" width="14.42578125" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -751,20 +759,20 @@
       <c r="Z2" s="4"/>
     </row>
     <row r="3" spans="1:26" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="8" t="s">
-        <v>0</v>
+      <c r="A3" s="27" t="s">
+        <v>21</v>
       </c>
-      <c r="B3" s="9"/>
-      <c r="C3" s="9"/>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="9"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="9"/>
-      <c r="J3" s="9"/>
-      <c r="K3" s="9"/>
-      <c r="L3" s="9"/>
+      <c r="B3" s="28"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="28"/>
+      <c r="H3" s="28"/>
+      <c r="I3" s="28"/>
+      <c r="J3" s="28"/>
+      <c r="K3" s="28"/>
+      <c r="L3" s="28"/>
       <c r="M3" s="4"/>
       <c r="N3" s="4"/>
       <c r="O3" s="4"/>
@@ -781,94 +789,94 @@
       <c r="Z3" s="4"/>
     </row>
     <row r="4" spans="1:26" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="30" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="31"/>
+      <c r="C4" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8"/>
+      <c r="K4" s="8"/>
+      <c r="L4" s="8"/>
+      <c r="M4" s="10"/>
+      <c r="N4" s="10"/>
+      <c r="O4" s="10"/>
+      <c r="P4" s="10"/>
+      <c r="Q4" s="10"/>
+      <c r="R4" s="10"/>
+      <c r="S4" s="10"/>
+      <c r="T4" s="10"/>
+      <c r="U4" s="10"/>
+      <c r="V4" s="10"/>
+      <c r="W4" s="10"/>
+      <c r="X4" s="10"/>
+      <c r="Y4" s="10"/>
+      <c r="Z4" s="10"/>
+    </row>
+    <row r="5" spans="1:26" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="25"/>
+      <c r="E5" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" s="25"/>
+      <c r="G5" s="13"/>
+      <c r="H5" s="14"/>
+      <c r="I5" s="14"/>
+      <c r="J5" s="14"/>
+      <c r="K5" s="14"/>
+      <c r="L5" s="14"/>
+      <c r="M5" s="10"/>
+      <c r="N5" s="10"/>
+      <c r="O5" s="10"/>
+      <c r="P5" s="10"/>
+      <c r="Q5" s="10"/>
+      <c r="R5" s="10"/>
+      <c r="S5" s="10"/>
+      <c r="T5" s="10"/>
+      <c r="U5" s="10"/>
+      <c r="V5" s="10"/>
+      <c r="W5" s="10"/>
+      <c r="X5" s="10"/>
+      <c r="Y5" s="10"/>
+      <c r="Z5" s="10"/>
+    </row>
+    <row r="6" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="15">
         <v>1</v>
       </c>
-      <c r="B4" s="11"/>
-      <c r="C4" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="13"/>
-      <c r="H4" s="14"/>
-      <c r="I4" s="13"/>
-      <c r="J4" s="13"/>
-      <c r="K4" s="13"/>
-      <c r="L4" s="13"/>
-      <c r="M4" s="15"/>
-      <c r="N4" s="15"/>
-      <c r="O4" s="15"/>
-      <c r="P4" s="15"/>
-      <c r="Q4" s="15"/>
-      <c r="R4" s="15"/>
-      <c r="S4" s="15"/>
-      <c r="T4" s="15"/>
-      <c r="U4" s="15"/>
-      <c r="V4" s="15"/>
-      <c r="W4" s="15"/>
-      <c r="X4" s="15"/>
-      <c r="Y4" s="15"/>
-      <c r="Z4" s="15"/>
-    </row>
-    <row r="5" spans="1:26" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="16" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="17" t="s">
-        <v>1</v>
-      </c>
-      <c r="C5" s="18" t="s">
-        <v>4</v>
-      </c>
-      <c r="D5" s="19"/>
-      <c r="E5" s="18" t="s">
-        <v>5</v>
-      </c>
-      <c r="F5" s="19"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="21"/>
-      <c r="I5" s="21"/>
-      <c r="J5" s="21"/>
-      <c r="K5" s="21"/>
-      <c r="L5" s="21"/>
-      <c r="M5" s="15"/>
-      <c r="N5" s="15"/>
-      <c r="O5" s="15"/>
-      <c r="P5" s="15"/>
-      <c r="Q5" s="15"/>
-      <c r="R5" s="15"/>
-      <c r="S5" s="15"/>
-      <c r="T5" s="15"/>
-      <c r="U5" s="15"/>
-      <c r="V5" s="15"/>
-      <c r="W5" s="15"/>
-      <c r="X5" s="15"/>
-      <c r="Y5" s="15"/>
-      <c r="Z5" s="15"/>
-    </row>
-    <row r="6" spans="1:26" ht="45" x14ac:dyDescent="0.25">
-      <c r="A6" s="22">
-        <v>1</v>
-      </c>
-      <c r="B6" s="23" t="s">
-        <v>6</v>
+      <c r="B6" s="16" t="s">
+        <v>27</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
-      <c r="D6" s="19"/>
+      <c r="D6" s="25"/>
       <c r="E6" s="24" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
-      <c r="F6" s="19"/>
-      <c r="G6" s="25"/>
-      <c r="H6" s="25"/>
-      <c r="I6" s="25"/>
-      <c r="J6" s="25"/>
-      <c r="K6" s="25"/>
-      <c r="L6" s="25"/>
+      <c r="F6" s="25"/>
+      <c r="G6" s="17"/>
+      <c r="H6" s="17"/>
+      <c r="I6" s="17"/>
+      <c r="J6" s="17"/>
+      <c r="K6" s="17"/>
+      <c r="L6" s="17"/>
       <c r="M6" s="4"/>
       <c r="N6" s="4"/>
       <c r="O6" s="4"/>
@@ -884,27 +892,27 @@
       <c r="Y6" s="4"/>
       <c r="Z6" s="4"/>
     </row>
-    <row r="7" spans="1:26" ht="45" x14ac:dyDescent="0.25">
-      <c r="A7" s="22">
+    <row r="7" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="15">
         <v>2</v>
       </c>
-      <c r="B7" s="23" t="s">
-        <v>9</v>
+      <c r="B7" s="16" t="s">
+        <v>30</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
-      <c r="D7" s="19"/>
+      <c r="D7" s="25"/>
       <c r="E7" s="24" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
-      <c r="F7" s="19"/>
-      <c r="G7" s="25"/>
-      <c r="H7" s="25"/>
-      <c r="I7" s="25"/>
-      <c r="J7" s="25"/>
-      <c r="K7" s="25"/>
-      <c r="L7" s="25"/>
+      <c r="F7" s="25"/>
+      <c r="G7" s="17"/>
+      <c r="H7" s="17"/>
+      <c r="I7" s="17"/>
+      <c r="J7" s="17"/>
+      <c r="K7" s="17"/>
+      <c r="L7" s="17"/>
       <c r="M7" s="4"/>
       <c r="N7" s="4"/>
       <c r="O7" s="4"/>
@@ -920,27 +928,27 @@
       <c r="Y7" s="4"/>
       <c r="Z7" s="4"/>
     </row>
-    <row r="8" spans="1:26" ht="45" x14ac:dyDescent="0.25">
-      <c r="A8" s="22">
+    <row r="8" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="15">
         <v>3</v>
       </c>
-      <c r="B8" s="23" t="s">
-        <v>10</v>
+      <c r="B8" s="16" t="s">
+        <v>31</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
-      <c r="D8" s="19"/>
+      <c r="D8" s="25"/>
       <c r="E8" s="24" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
-      <c r="F8" s="19"/>
-      <c r="G8" s="25"/>
-      <c r="H8" s="25"/>
-      <c r="I8" s="25"/>
-      <c r="J8" s="25"/>
-      <c r="K8" s="25"/>
-      <c r="L8" s="25"/>
+      <c r="F8" s="25"/>
+      <c r="G8" s="17"/>
+      <c r="H8" s="17"/>
+      <c r="I8" s="17"/>
+      <c r="J8" s="17"/>
+      <c r="K8" s="17"/>
+      <c r="L8" s="17"/>
       <c r="M8" s="4"/>
       <c r="N8" s="4"/>
       <c r="O8" s="4"/>
@@ -956,27 +964,27 @@
       <c r="Y8" s="4"/>
       <c r="Z8" s="4"/>
     </row>
-    <row r="9" spans="1:26" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="22">
+    <row r="9" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="15">
         <v>4</v>
       </c>
-      <c r="B9" s="23" t="s">
-        <v>12</v>
+      <c r="B9" s="16" t="s">
+        <v>32</v>
       </c>
       <c r="C9" s="24" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
-      <c r="D9" s="19"/>
+      <c r="D9" s="25"/>
       <c r="E9" s="24" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
-      <c r="F9" s="19"/>
-      <c r="G9" s="25"/>
-      <c r="H9" s="25"/>
-      <c r="I9" s="25"/>
-      <c r="J9" s="25"/>
-      <c r="K9" s="25"/>
-      <c r="L9" s="25"/>
+      <c r="F9" s="25"/>
+      <c r="G9" s="17"/>
+      <c r="H9" s="17"/>
+      <c r="I9" s="17"/>
+      <c r="J9" s="17"/>
+      <c r="K9" s="17"/>
+      <c r="L9" s="17"/>
       <c r="M9" s="4"/>
       <c r="N9" s="4"/>
       <c r="O9" s="4"/>
@@ -992,27 +1000,27 @@
       <c r="Y9" s="4"/>
       <c r="Z9" s="4"/>
     </row>
-    <row r="10" spans="1:26" ht="45" x14ac:dyDescent="0.25">
-      <c r="A10" s="22">
+    <row r="10" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="15">
         <v>5</v>
       </c>
-      <c r="B10" s="23" t="s">
-        <v>13</v>
+      <c r="B10" s="16" t="s">
+        <v>33</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
-      <c r="D10" s="19"/>
+      <c r="D10" s="25"/>
       <c r="E10" s="24" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
-      <c r="F10" s="19"/>
-      <c r="G10" s="25"/>
-      <c r="H10" s="25"/>
-      <c r="I10" s="25"/>
-      <c r="J10" s="25"/>
-      <c r="K10" s="25"/>
-      <c r="L10" s="25"/>
+      <c r="F10" s="25"/>
+      <c r="G10" s="17"/>
+      <c r="H10" s="17"/>
+      <c r="I10" s="17"/>
+      <c r="J10" s="17"/>
+      <c r="K10" s="17"/>
+      <c r="L10" s="17"/>
       <c r="M10" s="4"/>
       <c r="N10" s="4"/>
       <c r="O10" s="4"/>
@@ -1028,27 +1036,27 @@
       <c r="Y10" s="4"/>
       <c r="Z10" s="4"/>
     </row>
-    <row r="11" spans="1:26" ht="45" x14ac:dyDescent="0.25">
-      <c r="A11" s="22">
+    <row r="11" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="15">
         <v>6</v>
       </c>
-      <c r="B11" s="23" t="s">
-        <v>14</v>
+      <c r="B11" s="16" t="s">
+        <v>34</v>
       </c>
       <c r="C11" s="24" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
-      <c r="D11" s="19"/>
+      <c r="D11" s="25"/>
       <c r="E11" s="24" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
-      <c r="F11" s="19"/>
-      <c r="G11" s="25"/>
-      <c r="H11" s="25"/>
-      <c r="I11" s="25"/>
-      <c r="J11" s="25"/>
-      <c r="K11" s="25"/>
-      <c r="L11" s="25"/>
+      <c r="F11" s="25"/>
+      <c r="G11" s="17"/>
+      <c r="H11" s="17"/>
+      <c r="I11" s="17"/>
+      <c r="J11" s="17"/>
+      <c r="K11" s="17"/>
+      <c r="L11" s="17"/>
       <c r="M11" s="4"/>
       <c r="N11" s="4"/>
       <c r="O11" s="4"/>
@@ -1064,27 +1072,27 @@
       <c r="Y11" s="4"/>
       <c r="Z11" s="4"/>
     </row>
-    <row r="12" spans="1:26" ht="45" x14ac:dyDescent="0.25">
-      <c r="A12" s="22">
+    <row r="12" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="15">
         <v>7</v>
       </c>
-      <c r="B12" s="23" t="s">
-        <v>15</v>
+      <c r="B12" s="16" t="s">
+        <v>35</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
-      <c r="D12" s="19"/>
+      <c r="D12" s="25"/>
       <c r="E12" s="24" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
-      <c r="F12" s="19"/>
-      <c r="G12" s="25"/>
-      <c r="H12" s="25"/>
-      <c r="I12" s="25"/>
-      <c r="J12" s="25"/>
-      <c r="K12" s="25"/>
-      <c r="L12" s="25"/>
+      <c r="F12" s="25"/>
+      <c r="G12" s="17"/>
+      <c r="H12" s="17"/>
+      <c r="I12" s="17"/>
+      <c r="J12" s="17"/>
+      <c r="K12" s="17"/>
+      <c r="L12" s="17"/>
       <c r="M12" s="4"/>
       <c r="N12" s="4"/>
       <c r="O12" s="4"/>
@@ -1100,27 +1108,27 @@
       <c r="Y12" s="4"/>
       <c r="Z12" s="4"/>
     </row>
-    <row r="13" spans="1:26" ht="45" x14ac:dyDescent="0.25">
-      <c r="A13" s="22">
+    <row r="13" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="15">
         <v>8</v>
       </c>
-      <c r="B13" s="23" t="s">
-        <v>16</v>
+      <c r="B13" s="16" t="s">
+        <v>36</v>
       </c>
       <c r="C13" s="24" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
-      <c r="D13" s="19"/>
+      <c r="D13" s="25"/>
       <c r="E13" s="24" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
-      <c r="F13" s="19"/>
-      <c r="G13" s="25"/>
-      <c r="H13" s="25"/>
-      <c r="I13" s="25"/>
-      <c r="J13" s="25"/>
-      <c r="K13" s="25"/>
-      <c r="L13" s="25"/>
+      <c r="F13" s="25"/>
+      <c r="G13" s="17"/>
+      <c r="H13" s="17"/>
+      <c r="I13" s="17"/>
+      <c r="J13" s="17"/>
+      <c r="K13" s="17"/>
+      <c r="L13" s="17"/>
       <c r="M13" s="4"/>
       <c r="N13" s="4"/>
       <c r="O13" s="4"/>
@@ -1136,27 +1144,27 @@
       <c r="Y13" s="4"/>
       <c r="Z13" s="4"/>
     </row>
-    <row r="14" spans="1:26" ht="45" x14ac:dyDescent="0.25">
-      <c r="A14" s="22">
+    <row r="14" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="15">
         <v>9</v>
       </c>
-      <c r="B14" s="23" t="s">
-        <v>17</v>
+      <c r="B14" s="16" t="s">
+        <v>37</v>
       </c>
       <c r="C14" s="24" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
-      <c r="D14" s="19"/>
+      <c r="D14" s="25"/>
       <c r="E14" s="24" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
-      <c r="F14" s="19"/>
-      <c r="G14" s="25"/>
-      <c r="H14" s="25"/>
-      <c r="I14" s="25"/>
-      <c r="J14" s="25"/>
-      <c r="K14" s="25"/>
-      <c r="L14" s="25"/>
+      <c r="F14" s="25"/>
+      <c r="G14" s="17"/>
+      <c r="H14" s="17"/>
+      <c r="I14" s="17"/>
+      <c r="J14" s="17"/>
+      <c r="K14" s="17"/>
+      <c r="L14" s="17"/>
       <c r="M14" s="4"/>
       <c r="N14" s="4"/>
       <c r="O14" s="4"/>
@@ -1172,27 +1180,27 @@
       <c r="Y14" s="4"/>
       <c r="Z14" s="4"/>
     </row>
-    <row r="15" spans="1:26" ht="30" x14ac:dyDescent="0.25">
-      <c r="A15" s="22">
+    <row r="15" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="15">
         <v>10</v>
       </c>
-      <c r="B15" s="23" t="s">
-        <v>18</v>
+      <c r="B15" s="16" t="s">
+        <v>38</v>
       </c>
       <c r="C15" s="24" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
-      <c r="D15" s="19"/>
+      <c r="D15" s="25"/>
       <c r="E15" s="24" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
-      <c r="F15" s="19"/>
-      <c r="G15" s="25"/>
-      <c r="H15" s="25"/>
-      <c r="I15" s="25"/>
-      <c r="J15" s="25"/>
-      <c r="K15" s="25"/>
-      <c r="L15" s="25"/>
+      <c r="F15" s="25"/>
+      <c r="G15" s="17"/>
+      <c r="H15" s="17"/>
+      <c r="I15" s="17"/>
+      <c r="J15" s="17"/>
+      <c r="K15" s="17"/>
+      <c r="L15" s="17"/>
       <c r="M15" s="4"/>
       <c r="N15" s="4"/>
       <c r="O15" s="4"/>
@@ -1237,20 +1245,20 @@
       <c r="Z16" s="4"/>
     </row>
     <row r="17" spans="1:26" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="26" t="s">
-        <v>19</v>
+      <c r="A17" s="32" t="s">
+        <v>39</v>
       </c>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="9"/>
-      <c r="J17" s="9"/>
-      <c r="K17" s="9"/>
-      <c r="L17" s="9"/>
+      <c r="B17" s="28"/>
+      <c r="C17" s="28"/>
+      <c r="D17" s="28"/>
+      <c r="E17" s="28"/>
+      <c r="F17" s="28"/>
+      <c r="G17" s="28"/>
+      <c r="H17" s="28"/>
+      <c r="I17" s="28"/>
+      <c r="J17" s="28"/>
+      <c r="K17" s="28"/>
+      <c r="L17" s="28"/>
       <c r="M17" s="4"/>
       <c r="N17" s="4"/>
       <c r="O17" s="4"/>
@@ -1267,18 +1275,18 @@
       <c r="Z17" s="4"/>
     </row>
     <row r="18" spans="1:26" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="9"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="9"/>
-      <c r="J18" s="9"/>
-      <c r="K18" s="9"/>
-      <c r="L18" s="9"/>
+      <c r="A18" s="28"/>
+      <c r="B18" s="28"/>
+      <c r="C18" s="28"/>
+      <c r="D18" s="28"/>
+      <c r="E18" s="28"/>
+      <c r="F18" s="28"/>
+      <c r="G18" s="28"/>
+      <c r="H18" s="28"/>
+      <c r="I18" s="28"/>
+      <c r="J18" s="28"/>
+      <c r="K18" s="28"/>
+      <c r="L18" s="28"/>
       <c r="M18" s="4"/>
       <c r="N18" s="4"/>
       <c r="O18" s="4"/>
@@ -1295,18 +1303,18 @@
       <c r="Z18" s="4"/>
     </row>
     <row r="19" spans="1:26" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="9"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="9"/>
-      <c r="J19" s="9"/>
-      <c r="K19" s="9"/>
-      <c r="L19" s="9"/>
+      <c r="A19" s="28"/>
+      <c r="B19" s="28"/>
+      <c r="C19" s="28"/>
+      <c r="D19" s="28"/>
+      <c r="E19" s="28"/>
+      <c r="F19" s="28"/>
+      <c r="G19" s="28"/>
+      <c r="H19" s="28"/>
+      <c r="I19" s="28"/>
+      <c r="J19" s="28"/>
+      <c r="K19" s="28"/>
+      <c r="L19" s="28"/>
       <c r="M19" s="4"/>
       <c r="N19" s="4"/>
       <c r="O19" s="4"/>
@@ -1323,18 +1331,18 @@
       <c r="Z19" s="4"/>
     </row>
     <row r="20" spans="1:26" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="9"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="9"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="9"/>
-      <c r="J20" s="9"/>
-      <c r="K20" s="9"/>
-      <c r="L20" s="9"/>
+      <c r="A20" s="28"/>
+      <c r="B20" s="28"/>
+      <c r="C20" s="28"/>
+      <c r="D20" s="28"/>
+      <c r="E20" s="28"/>
+      <c r="F20" s="28"/>
+      <c r="G20" s="28"/>
+      <c r="H20" s="28"/>
+      <c r="I20" s="28"/>
+      <c r="J20" s="28"/>
+      <c r="K20" s="28"/>
+      <c r="L20" s="28"/>
       <c r="M20" s="4"/>
       <c r="N20" s="4"/>
       <c r="O20" s="4"/>
@@ -28819,12 +28827,16 @@
     <mergeCell ref="E15:F15"/>
     <mergeCell ref="C13:D13"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="70" orientation="landscape" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:Z1000"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -28833,12 +28845,13 @@
     <col min="3" max="3" width="4.42578125" style="5" customWidth="1"/>
     <col min="4" max="6" width="11.42578125" style="5" customWidth="1"/>
     <col min="7" max="26" width="10" style="5" customWidth="1"/>
-    <col min="27" max="16384" width="14.42578125" style="5"/>
+    <col min="27" max="27" width="14.42578125" style="5" customWidth="1"/>
+    <col min="28" max="16384" width="14.42578125" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="27" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="27" t="s">
-        <v>20</v>
+      <c r="A1" s="18" t="s">
+        <v>0</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -28867,8 +28880,8 @@
       <c r="Z1" s="4"/>
     </row>
     <row r="2" spans="1:26" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="28" t="s">
-        <v>21</v>
+      <c r="A2" s="19" t="s">
+        <v>1</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -28925,8 +28938,8 @@
       <c r="Z3" s="4"/>
     </row>
     <row r="4" spans="1:26" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="29" t="s">
-        <v>22</v>
+      <c r="A4" s="20" t="s">
+        <v>2</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -28955,11 +28968,11 @@
       <c r="Z4" s="4"/>
     </row>
     <row r="5" spans="1:26" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="30" t="s">
-        <v>23</v>
+      <c r="A5" s="21" t="s">
+        <v>3</v>
       </c>
-      <c r="B5" s="30" t="s">
-        <v>21</v>
+      <c r="B5" s="21" t="s">
+        <v>1</v>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
@@ -28987,12 +29000,12 @@
       <c r="Z5" s="4"/>
     </row>
     <row r="6" spans="1:26" ht="53.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="31" t="str">
+      <c r="A6" s="22" t="str">
         <f>'Recursos x Actividad'!A5</f>
         <v>ID Actividad</v>
       </c>
-      <c r="B6" s="32" t="s">
-        <v>24</v>
+      <c r="B6" s="23" t="s">
+        <v>4</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
@@ -29020,12 +29033,12 @@
       <c r="Z6" s="4"/>
     </row>
     <row r="7" spans="1:26" ht="36.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="31" t="str">
+      <c r="A7" s="22" t="str">
         <f>'Recursos x Actividad'!B5</f>
         <v>Actividad</v>
       </c>
-      <c r="B7" s="32" t="s">
-        <v>25</v>
+      <c r="B7" s="23" t="s">
+        <v>5</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
@@ -29053,11 +29066,11 @@
       <c r="Z7" s="4"/>
     </row>
     <row r="8" spans="1:26" ht="52.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="31" t="s">
-        <v>26</v>
+      <c r="A8" s="22" t="s">
+        <v>6</v>
       </c>
-      <c r="B8" s="32" t="s">
-        <v>27</v>
+      <c r="B8" s="23" t="s">
+        <v>7</v>
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
@@ -29085,11 +29098,11 @@
       <c r="Z8" s="4"/>
     </row>
     <row r="9" spans="1:26" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="31" t="s">
-        <v>28</v>
+      <c r="A9" s="22" t="s">
+        <v>8</v>
       </c>
-      <c r="B9" s="32" t="s">
-        <v>29</v>
+      <c r="B9" s="23" t="s">
+        <v>9</v>
       </c>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
@@ -29145,8 +29158,8 @@
       <c r="Z10" s="4"/>
     </row>
     <row r="11" spans="1:26" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="29" t="s">
-        <v>30</v>
+      <c r="A11" s="20" t="s">
+        <v>10</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
@@ -29175,11 +29188,11 @@
       <c r="Z11" s="4"/>
     </row>
     <row r="12" spans="1:26" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="30" t="s">
-        <v>31</v>
+      <c r="A12" s="21" t="s">
+        <v>11</v>
       </c>
-      <c r="B12" s="30" t="s">
-        <v>32</v>
+      <c r="B12" s="21" t="s">
+        <v>12</v>
       </c>
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
@@ -29206,12 +29219,12 @@
       <c r="Y12" s="4"/>
       <c r="Z12" s="4"/>
     </row>
-    <row r="13" spans="1:26" ht="30" x14ac:dyDescent="0.25">
-      <c r="A13" s="31" t="s">
-        <v>33</v>
+    <row r="13" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="22" t="s">
+        <v>13</v>
       </c>
-      <c r="B13" s="32" t="s">
-        <v>34</v>
+      <c r="B13" s="23" t="s">
+        <v>14</v>
       </c>
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
@@ -29238,12 +29251,12 @@
       <c r="Y13" s="4"/>
       <c r="Z13" s="4"/>
     </row>
-    <row r="14" spans="1:26" ht="60" x14ac:dyDescent="0.25">
-      <c r="A14" s="31" t="s">
-        <v>35</v>
+    <row r="14" spans="1:26" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="22" t="s">
+        <v>15</v>
       </c>
-      <c r="B14" s="32" t="s">
-        <v>36</v>
+      <c r="B14" s="23" t="s">
+        <v>16</v>
       </c>
       <c r="C14" s="4"/>
       <c r="D14" s="4"/>
@@ -29270,12 +29283,12 @@
       <c r="Y14" s="4"/>
       <c r="Z14" s="4"/>
     </row>
-    <row r="15" spans="1:26" ht="30" x14ac:dyDescent="0.25">
-      <c r="A15" s="31" t="s">
-        <v>11</v>
+    <row r="15" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="22" t="s">
+        <v>17</v>
       </c>
-      <c r="B15" s="32" t="s">
-        <v>37</v>
+      <c r="B15" s="23" t="s">
+        <v>18</v>
       </c>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
@@ -29302,12 +29315,12 @@
       <c r="Y15" s="4"/>
       <c r="Z15" s="4"/>
     </row>
-    <row r="16" spans="1:26" ht="30" x14ac:dyDescent="0.25">
-      <c r="A16" s="31" t="s">
-        <v>38</v>
+    <row r="16" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="22" t="s">
+        <v>19</v>
       </c>
-      <c r="B16" s="32" t="s">
-        <v>39</v>
+      <c r="B16" s="23" t="s">
+        <v>20</v>
       </c>
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
@@ -56887,6 +56900,7 @@
       <c r="Z1000" s="4"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="90" orientation="landscape" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
--- a/Fase 2/Evidencias Proyecto/Evidencias de Documentación/Matriz RACI CuTuCo.xlsx
+++ b/Fase 2/Evidencias Proyecto/Evidencias de Documentación/Matriz RACI CuTuCo.xlsx
@@ -133,16 +133,16 @@
     <t>Fase 2 - ERS con el alcance actualizado (Queda / No queda), criterios de aceptación y Plan de Calidad y de Costos (Semanas 2-4)</t>
   </si>
   <si>
-    <t>Fase 2 - Modelo de datos (DER, tablas productores y payments, RLS) y arquitectura: Supabase (GoTrue, PostgREST), FastAPI y despliegue (Semanas 2-4)</t>
+    <t>Fase 2 - Modelo de datos (MER, tablas productores y payments, RLS) y arquitectura: Supabase (GoTrue, PostgREST), FastAPI solo para la integración con Webpay y despliegue (Semanas 2-4)</t>
   </si>
   <si>
     <t>Fase 2 - Mockups de interfaz en Vue.js: cliente, productor, administración, checkout y entrega (Semanas 3-4)</t>
   </si>
   <si>
-    <t>Fase 3 - Backend: autenticación con GoTrue, bloqueo tras 5 intentos, reglas de negocio y pagos en FastAPI, entrega con código (Semanas 4-10)</t>
+    <t>Fase 3 - Backend: autenticación y autorización con Supabase Auth (GoTrue) mediante roles, RLS, policies y grants, integración con Webpay Mall (Split Payment) en FastAPI, gestión de reclamos y sanciones, y entrega con código (Semanas 4-10)</t>
   </si>
   <si>
-    <t>Fase 3 - Frontend: Vue.js/Vite, catálogo invitado, carrito, panel del productor, administración, checkout y seguimiento (Semanas 4-10)</t>
+    <t>Fase 3 - Frontend: Vue.js/Vite, catálogo invitado, carrito, panel del productor, administración (aprobaciones, reclamos y sanciones), checkout y seguimiento (Semanas 4-10)</t>
   </si>
   <si>
     <t>Fase 3 - Base de datos e integraciones: migración SQLite a PostgreSQL, scripts DDL, Webpay Mall (Split Payment) y correos con Resend (Semanas 4-10)</t>
@@ -157,7 +157,7 @@
     <t>Fase 4 - Plan de Pruebas Final, Reporte de Estatus Final, cierre y preparación de la entrega final (Semanas 12-13)</t>
   </si>
   <si>
-    <t>Criterio de asignación: somos dos personas y repartimos las responsabilidades según la especialidad de cada uno. Vicente lidera backend, pagos, base de datos y las decisiones de proyecto; Ignacio lidera frontend, mockups y pantallas. Arquitectura, pruebas, documentación y control de cambios los trabajamos juntos. Como solo hay dos integrantes, usamos "A/R" cuando la misma persona ejecuta y aprueba, y "R" cuando el otro integrante también ejecuta. El alcance actualizado dejó fuera el historial de precios, los avisos de stock bajo, los múltiples administradores, la retención de carnet y el rate limiting, por lo que no tienen actividad propia. La segunda redefinición de alcance reemplazó además el escrow manual y los payouts por Webpay Mall (Split Payment) con liquidación directa por pasarela, e incorporó la verificación documental KYB y el ingreso del Código de Comercio Mall en la aprobación de vendedores. R = Responsable de ejecutar; A = Aprobador; C = Consultado; I = Informado.</t>
+    <t>Criterio de asignación: somos dos personas y repartimos las responsabilidades según la especialidad de cada uno. Vicente lidera backend, pagos, base de datos y las decisiones de proyecto; Ignacio lidera frontend, mockups y pantallas. Arquitectura, pruebas, documentación y control de cambios los trabajamos juntos. Como solo hay dos integrantes, usamos "A/R" cuando la misma persona ejecuta y aprueba, y "R" cuando el otro integrante también ejecuta. El alcance vigente deja fuera el historial de precios, los avisos de stock bajo, los múltiples administradores, el almacenamiento de datos sensibles (RF-015) y el rate limiting propio, por lo que no tienen actividad propia. El pago funciona con Webpay Mall (Split Payment): la pasarela captura y dispersa el pago en tiempo real y Transbank deposita directo en la cuenta bancaria del comercio, de modo que CuTuCo no administra fondos de terceros. La autenticación y las autorizaciones se gestionan con Supabase Auth (GoTrue) y con roles, RLS, policies y grants; FastAPI se limita a la lógica específica y compleja de la integración con Webpay. La validación de palabras prohibidas es automática, mediante triggers de PostgreSQL (incluida la lógica BEFORE INSERT ya existente), sin intervención operativa del administrador. Aprobar o rechazar una postulación y registrar el Código de Comercio Mall son dos procesos distintos: el código se registra cuando se completa el trámite con Transbank y, mientras el productor no lo tenga registrado, no puede operar. La actualización incorporó la verificación documental KYB y la gestión de reclamos (RF-027), con sanciones y apelaciones. R = Responsable de ejecutar; A = Aprobador; C = Consultado; I = Informado.</t>
   </si>
 </sst>
 </file>
